--- a/patterns/results/exp2/go-tradeoffs-results.xlsx
+++ b/patterns/results/exp2/go-tradeoffs-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0E67E9-DF67-074B-8A45-0ECA756FEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FA470F-8B2A-F543-84EB-A6BC41711F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="1100" windowWidth="34460" windowHeight="16660" activeTab="2" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="3360" yWindow="1060" windowWidth="34460" windowHeight="16660" activeTab="1" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO-2BINS" sheetId="1" r:id="rId1"/>
@@ -172,7 +172,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -249,13 +249,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="9"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -659,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -745,8 +738,6 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -799,7 +790,6 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1519,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="64"/>
-      <c r="E6" s="81">
+      <c r="E6" s="79">
         <v>0.11111111111111099</v>
       </c>
       <c r="F6" s="55">
@@ -1561,7 +1551,7 @@
       <c r="F7" s="55">
         <v>0</v>
       </c>
-      <c r="G7" s="79">
+      <c r="G7" s="77">
         <v>0</v>
       </c>
       <c r="H7" s="55"/>
@@ -1597,7 +1587,7 @@
       <c r="F8" s="47">
         <v>1</v>
       </c>
-      <c r="G8" s="80">
+      <c r="G8" s="78">
         <v>0</v>
       </c>
       <c r="H8" s="55"/>
@@ -1630,7 +1620,7 @@
       <c r="E9" s="55">
         <v>0</v>
       </c>
-      <c r="F9" s="81">
+      <c r="F9" s="79">
         <v>0</v>
       </c>
       <c r="G9" s="71">
@@ -1666,7 +1656,7 @@
       <c r="E10" s="44">
         <v>0</v>
       </c>
-      <c r="F10" s="82">
+      <c r="F10" s="80">
         <v>0</v>
       </c>
       <c r="G10" s="71">
@@ -1695,7 +1685,7 @@
       <c r="B11" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="111" t="s">
+      <c r="C11" s="109" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="64"/>
@@ -1741,7 +1731,7 @@
       <c r="F12" s="55">
         <v>0</v>
       </c>
-      <c r="G12" s="81">
+      <c r="G12" s="79">
         <v>0.88888888888888795</v>
       </c>
       <c r="H12" s="55"/>
@@ -1767,7 +1757,7 @@
       <c r="B13" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="112" t="s">
+      <c r="C13" s="110" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="64"/>
@@ -1777,7 +1767,7 @@
       <c r="F13" s="55">
         <v>0</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="81">
         <v>0</v>
       </c>
       <c r="H13" s="55"/>
@@ -1803,10 +1793,10 @@
       <c r="B14" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="113" t="s">
+      <c r="C14" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="84"/>
+      <c r="D14" s="82"/>
       <c r="E14" s="38">
         <v>0</v>
       </c>
@@ -1839,14 +1829,14 @@
       <c r="B15" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="87"/>
+      <c r="D15" s="85"/>
       <c r="E15" s="55">
         <v>0</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="79">
         <v>0</v>
       </c>
       <c r="G15" s="71">
@@ -1875,14 +1865,14 @@
       <c r="B16" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="113" t="s">
+      <c r="C16" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="85"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="44">
         <v>0</v>
       </c>
-      <c r="F16" s="82">
+      <c r="F16" s="80">
         <v>0</v>
       </c>
       <c r="G16" s="71">
@@ -1911,10 +1901,10 @@
       <c r="B17" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="114" t="s">
+      <c r="C17" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="86"/>
+      <c r="D17" s="84"/>
       <c r="E17" s="46">
         <v>0</v>
       </c>
@@ -1947,17 +1937,17 @@
       <c r="B18" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="87"/>
+      <c r="D18" s="85"/>
       <c r="E18" s="55">
         <v>0</v>
       </c>
       <c r="F18" s="55">
         <v>0</v>
       </c>
-      <c r="G18" s="88">
+      <c r="G18" s="86">
         <v>1</v>
       </c>
       <c r="H18" s="55"/>
@@ -1983,7 +1973,7 @@
       <c r="B19" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="116" t="s">
+      <c r="C19" s="114" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="26"/>
@@ -1993,7 +1983,7 @@
       <c r="F19" s="17">
         <v>1</v>
       </c>
-      <c r="G19" s="82">
+      <c r="G19" s="80">
         <v>0</v>
       </c>
       <c r="H19" s="55"/>
@@ -2480,25 +2470,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="90" t="s">
+      <c r="A1" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="90" t="s">
+      <c r="D1" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="E1" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="90" t="s">
+      <c r="F1" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="89" t="s">
         <v>16</v>
       </c>
       <c r="H1" s="53"/>
@@ -2522,7 +2512,7 @@
       <c r="B2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="96"/>
+      <c r="C2" s="94"/>
       <c r="D2" s="39">
         <v>0</v>
       </c>
@@ -2532,7 +2522,7 @@
       <c r="F2" s="39">
         <v>0</v>
       </c>
-      <c r="G2" s="103">
+      <c r="G2" s="101">
         <v>1</v>
       </c>
       <c r="H2" s="55"/>
@@ -2550,13 +2540,13 @@
       <c r="T2" s="56"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="95" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="93"/>
+      <c r="C3" s="91"/>
       <c r="D3" s="56">
         <v>0</v>
       </c>
@@ -2566,7 +2556,7 @@
       <c r="F3" s="74">
         <v>0.55555555555555503</v>
       </c>
-      <c r="G3" s="98">
+      <c r="G3" s="96">
         <v>0</v>
       </c>
       <c r="H3" s="55"/>
@@ -2590,7 +2580,7 @@
       <c r="B4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="93"/>
+      <c r="C4" s="91"/>
       <c r="D4" s="74">
         <v>7.1428571428571397E-2</v>
       </c>
@@ -2600,7 +2590,7 @@
       <c r="F4" s="74">
         <v>0.28571428571428498</v>
       </c>
-      <c r="G4" s="98">
+      <c r="G4" s="96">
         <v>0</v>
       </c>
       <c r="H4" s="55"/>
@@ -2618,13 +2608,13 @@
       <c r="T4" s="56"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="100" t="s">
+      <c r="A5" s="98" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="106" t="s">
+      <c r="C5" s="104" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="38">
@@ -2654,19 +2644,19 @@
       <c r="T5" s="56"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="95" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="107" t="s">
+      <c r="C6" s="105" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="55">
         <v>0</v>
       </c>
-      <c r="E6" s="83">
+      <c r="E6" s="81">
         <v>0</v>
       </c>
       <c r="F6" s="55">
@@ -2690,7 +2680,7 @@
       <c r="T6" s="56"/>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="99" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="54" t="s">
@@ -2702,13 +2692,13 @@
       <c r="D7" s="44">
         <v>0.14285714285714199</v>
       </c>
-      <c r="E7" s="105">
+      <c r="E7" s="103">
         <v>0.85714285714285698</v>
       </c>
-      <c r="F7" s="44">
-        <v>0</v>
-      </c>
-      <c r="G7" s="79">
+      <c r="F7" s="55">
+        <v>0</v>
+      </c>
+      <c r="G7" s="77">
         <v>0</v>
       </c>
       <c r="H7" s="55"/>
@@ -2719,13 +2709,13 @@
       <c r="T7" s="56"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="99" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="108" t="s">
+      <c r="C8" s="106" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="46">
@@ -2734,10 +2724,10 @@
       <c r="E8" s="55">
         <v>0</v>
       </c>
-      <c r="F8" s="77">
-        <v>0</v>
-      </c>
-      <c r="G8" s="80">
+      <c r="F8" s="47">
+        <v>0</v>
+      </c>
+      <c r="G8" s="78">
         <v>0</v>
       </c>
       <c r="H8" s="55"/>
@@ -2748,13 +2738,13 @@
       <c r="T8" s="56"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="99" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="109" t="s">
+      <c r="C9" s="107" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="55">
@@ -2763,7 +2753,7 @@
       <c r="E9" s="67">
         <v>0.44444444444444398</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="79">
         <v>0.55555555555555503</v>
       </c>
       <c r="G9" s="71">
@@ -2792,7 +2782,7 @@
       <c r="E10" s="44">
         <v>0</v>
       </c>
-      <c r="F10" s="78">
+      <c r="F10" s="80">
         <v>0</v>
       </c>
       <c r="G10" s="71">
@@ -2812,7 +2802,7 @@
       <c r="B11" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="110" t="s">
+      <c r="C11" s="108" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="55">
@@ -2853,7 +2843,7 @@
       <c r="F12" s="55">
         <v>0</v>
       </c>
-      <c r="G12" s="81">
+      <c r="G12" s="79">
         <v>0</v>
       </c>
       <c r="H12" s="55"/>
@@ -3119,7 +3109,7 @@
       <c r="B2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="96"/>
+      <c r="C2" s="94"/>
       <c r="D2" s="38">
         <v>0</v>
       </c>
@@ -3129,7 +3119,7 @@
       <c r="F2" s="38">
         <v>0</v>
       </c>
-      <c r="G2" s="119">
+      <c r="G2" s="117">
         <v>1</v>
       </c>
       <c r="H2" s="38">
@@ -3151,14 +3141,14 @@
       <c r="T2" s="56"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="95" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="117">
+      <c r="C3" s="91"/>
+      <c r="D3" s="115">
         <v>0.77777777777777701</v>
       </c>
       <c r="E3" s="55">
@@ -3170,13 +3160,13 @@
       <c r="G3" s="55">
         <v>0</v>
       </c>
-      <c r="H3" s="117">
+      <c r="H3" s="115">
         <v>0.22222222222222199</v>
       </c>
       <c r="I3" s="56">
         <v>0</v>
       </c>
-      <c r="J3" s="120"/>
+      <c r="J3" s="118"/>
       <c r="K3" s="30"/>
       <c r="L3" s="56"/>
       <c r="M3" s="56"/>
@@ -3195,14 +3185,14 @@
       <c r="B4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="99"/>
+      <c r="C4" s="97"/>
       <c r="D4" s="43">
         <v>0</v>
       </c>
-      <c r="E4" s="118">
+      <c r="E4" s="116">
         <v>0.27272727272727199</v>
       </c>
-      <c r="F4" s="118">
+      <c r="F4" s="116">
         <v>0.63636363636363602</v>
       </c>
       <c r="G4" s="43">
@@ -3211,7 +3201,7 @@
       <c r="H4" s="43">
         <v>0</v>
       </c>
-      <c r="I4" s="118">
+      <c r="I4" s="116">
         <v>9.0909090909090898E-2</v>
       </c>
       <c r="J4" s="20"/>
@@ -3273,7 +3263,7 @@
       <c r="B6" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="94" t="s">
+      <c r="C6" s="92" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="22">
@@ -3294,7 +3284,7 @@
       <c r="I6" s="66">
         <v>0</v>
       </c>
-      <c r="J6" s="120"/>
+      <c r="J6" s="118"/>
       <c r="K6" s="30"/>
       <c r="L6" s="56"/>
       <c r="M6" s="60"/>
@@ -3313,7 +3303,7 @@
       <c r="B7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="121" t="s">
+      <c r="C7" s="119" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="34">
@@ -3334,7 +3324,7 @@
       <c r="I7" s="66">
         <v>0</v>
       </c>
-      <c r="J7" s="120"/>
+      <c r="J7" s="118"/>
       <c r="K7" s="30"/>
       <c r="L7" s="54"/>
       <c r="M7" s="54"/>
@@ -3347,7 +3337,7 @@
       <c r="T7" s="54"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="97" t="s">
+      <c r="A8" s="95" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="54" t="s">
@@ -3393,7 +3383,7 @@
       <c r="B9" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="92" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="66">
@@ -3414,7 +3404,7 @@
       <c r="I9" s="66">
         <v>0</v>
       </c>
-      <c r="J9" s="120"/>
+      <c r="J9" s="118"/>
       <c r="K9" s="30"/>
       <c r="L9" s="54"/>
       <c r="M9" s="54"/>
@@ -3433,7 +3423,7 @@
       <c r="B10" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="93" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="4">
@@ -3464,7 +3454,7 @@
       <c r="B11" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="100" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="2">
@@ -3476,7 +3466,7 @@
       <c r="F11" s="32">
         <v>0</v>
       </c>
-      <c r="G11" s="124">
+      <c r="G11" s="121">
         <v>0</v>
       </c>
       <c r="H11" s="2">
@@ -3495,7 +3485,7 @@
       <c r="B12" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="92" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="66">
@@ -3507,7 +3497,7 @@
       <c r="F12" s="33">
         <v>0</v>
       </c>
-      <c r="G12" s="125">
+      <c r="G12" s="122">
         <v>0</v>
       </c>
       <c r="H12" s="66">
@@ -3516,7 +3506,7 @@
       <c r="I12" s="66">
         <v>0</v>
       </c>
-      <c r="J12" s="120"/>
+      <c r="J12" s="118"/>
       <c r="K12" s="30"/>
     </row>
     <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3526,7 +3516,7 @@
       <c r="B13" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="93" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="4">
@@ -3551,7 +3541,7 @@
       <c r="K13" s="31"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="97" t="s">
+      <c r="A14" s="95" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="54" t="s">
@@ -3588,7 +3578,7 @@
       <c r="B15" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="92" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="66">
@@ -3609,7 +3599,7 @@
       <c r="I15" s="66">
         <v>0</v>
       </c>
-      <c r="J15" s="120"/>
+      <c r="J15" s="118"/>
       <c r="K15" s="30"/>
     </row>
     <row r="16" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3619,7 +3609,7 @@
       <c r="B16" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="119" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="66">
@@ -3640,7 +3630,7 @@
       <c r="I16" s="66">
         <v>0</v>
       </c>
-      <c r="J16" s="120"/>
+      <c r="J16" s="118"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -3702,7 +3692,7 @@
       <c r="I18" s="66">
         <v>0</v>
       </c>
-      <c r="J18" s="120"/>
+      <c r="J18" s="118"/>
       <c r="K18" s="30"/>
     </row>
     <row r="19" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3712,7 +3702,7 @@
       <c r="B19" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="122" t="s">
+      <c r="C19" s="120" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="4">
@@ -3737,13 +3727,13 @@
       <c r="K19" s="31"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="95" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="102" t="s">
         <v>22</v>
       </c>
       <c r="D20" s="55">
@@ -3764,7 +3754,7 @@
       <c r="I20" s="47">
         <v>0</v>
       </c>
-      <c r="J20" s="120"/>
+      <c r="J20" s="118"/>
       <c r="K20" s="30"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -3774,7 +3764,7 @@
       <c r="B21" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="94" t="s">
+      <c r="C21" s="92" t="s">
         <v>22</v>
       </c>
       <c r="D21" s="66">
@@ -3795,7 +3785,7 @@
       <c r="I21" s="33">
         <v>0</v>
       </c>
-      <c r="J21" s="120"/>
+      <c r="J21" s="118"/>
       <c r="K21" s="30"/>
     </row>
     <row r="22" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3805,7 +3795,7 @@
       <c r="B22" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="95" t="s">
+      <c r="C22" s="93" t="s">
         <v>22</v>
       </c>
       <c r="D22" s="4">
@@ -3836,7 +3826,7 @@
       <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="102" t="s">
+      <c r="C23" s="100" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="32">
@@ -3867,10 +3857,10 @@
       <c r="B24" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="94" t="s">
+      <c r="C24" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="126">
+      <c r="D24" s="123">
         <v>1</v>
       </c>
       <c r="E24" s="65">
@@ -3888,7 +3878,7 @@
       <c r="I24" s="66">
         <v>0</v>
       </c>
-      <c r="J24" s="120"/>
+      <c r="J24" s="118"/>
       <c r="K24" s="30"/>
     </row>
     <row r="25" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3898,7 +3888,7 @@
       <c r="B25" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="92" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="34">
@@ -3919,7 +3909,7 @@
       <c r="I25" s="66">
         <v>0</v>
       </c>
-      <c r="J25" s="120"/>
+      <c r="J25" s="118"/>
       <c r="K25" s="30"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -3929,7 +3919,7 @@
       <c r="B26" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="94" t="s">
+      <c r="C26" s="92" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="66">
@@ -3950,7 +3940,7 @@
       <c r="I26" s="66">
         <v>0</v>
       </c>
-      <c r="J26" s="120"/>
+      <c r="J26" s="118"/>
       <c r="K26" s="30"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -3960,7 +3950,7 @@
       <c r="B27" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="92" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="66">
@@ -3981,7 +3971,7 @@
       <c r="I27" s="66">
         <v>0</v>
       </c>
-      <c r="J27" s="120"/>
+      <c r="J27" s="118"/>
       <c r="K27" s="30"/>
     </row>
     <row r="28" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3991,7 +3981,7 @@
       <c r="B28" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="94" t="s">
+      <c r="C28" s="92" t="s">
         <v>18</v>
       </c>
       <c r="D28" s="66">
@@ -4012,7 +4002,7 @@
       <c r="I28" s="66">
         <v>0</v>
       </c>
-      <c r="J28" s="120"/>
+      <c r="J28" s="118"/>
       <c r="K28" s="30"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -4022,7 +4012,7 @@
       <c r="B29" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="94" t="s">
+      <c r="C29" s="92" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="66">
@@ -4043,7 +4033,7 @@
       <c r="I29" s="66">
         <v>0</v>
       </c>
-      <c r="J29" s="120"/>
+      <c r="J29" s="118"/>
       <c r="K29" s="30"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -4053,7 +4043,7 @@
       <c r="B30" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="94" t="s">
+      <c r="C30" s="92" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="66">
@@ -4074,7 +4064,7 @@
       <c r="I30" s="66">
         <v>0</v>
       </c>
-      <c r="J30" s="120"/>
+      <c r="J30" s="118"/>
       <c r="K30" s="30"/>
     </row>
     <row r="31" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4084,7 +4074,7 @@
       <c r="B31" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="94" t="s">
+      <c r="C31" s="92" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="66">
@@ -4105,7 +4095,7 @@
       <c r="I31" s="66">
         <v>0</v>
       </c>
-      <c r="J31" s="120"/>
+      <c r="J31" s="118"/>
       <c r="K31" s="30"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -4115,7 +4105,7 @@
       <c r="B32" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="92" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="66">
@@ -4136,7 +4126,7 @@
       <c r="I32" s="66">
         <v>0</v>
       </c>
-      <c r="J32" s="120"/>
+      <c r="J32" s="118"/>
       <c r="K32" s="30"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -4146,7 +4136,7 @@
       <c r="B33" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="94" t="s">
+      <c r="C33" s="92" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="66">
@@ -4167,7 +4157,7 @@
       <c r="I33" s="66">
         <v>0</v>
       </c>
-      <c r="J33" s="120"/>
+      <c r="J33" s="118"/>
       <c r="K33" s="30"/>
     </row>
     <row r="34" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4177,7 +4167,7 @@
       <c r="B34" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="94" t="s">
+      <c r="C34" s="92" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="66">
@@ -4198,7 +4188,7 @@
       <c r="I34" s="66">
         <v>0</v>
       </c>
-      <c r="J34" s="120"/>
+      <c r="J34" s="118"/>
       <c r="K34" s="30"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -4208,7 +4198,7 @@
       <c r="B35" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="94" t="s">
+      <c r="C35" s="92" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="66">
@@ -4229,7 +4219,7 @@
       <c r="I35" s="66">
         <v>0</v>
       </c>
-      <c r="J35" s="120"/>
+      <c r="J35" s="118"/>
       <c r="K35" s="30"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -4239,7 +4229,7 @@
       <c r="B36" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="94" t="s">
+      <c r="C36" s="92" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="66">
@@ -4260,7 +4250,7 @@
       <c r="I36" s="66">
         <v>0</v>
       </c>
-      <c r="J36" s="120"/>
+      <c r="J36" s="118"/>
       <c r="K36" s="30"/>
     </row>
     <row r="37" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4270,7 +4260,7 @@
       <c r="B37" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="94" t="s">
+      <c r="C37" s="92" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="66">
@@ -4291,7 +4281,7 @@
       <c r="I37" s="66">
         <v>1</v>
       </c>
-      <c r="J37" s="120"/>
+      <c r="J37" s="118"/>
       <c r="K37" s="30"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -4301,7 +4291,7 @@
       <c r="B38" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="94" t="s">
+      <c r="C38" s="92" t="s">
         <v>22</v>
       </c>
       <c r="D38" s="66">
@@ -4322,7 +4312,7 @@
       <c r="I38" s="32">
         <v>0</v>
       </c>
-      <c r="J38" s="120"/>
+      <c r="J38" s="118"/>
       <c r="K38" s="30"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -4332,7 +4322,7 @@
       <c r="B39" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="94" t="s">
+      <c r="C39" s="92" t="s">
         <v>22</v>
       </c>
       <c r="D39" s="66">
@@ -4353,7 +4343,7 @@
       <c r="I39" s="33">
         <v>0</v>
       </c>
-      <c r="J39" s="120"/>
+      <c r="J39" s="118"/>
       <c r="K39" s="30"/>
     </row>
     <row r="40" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4363,7 +4353,7 @@
       <c r="B40" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="95" t="s">
+      <c r="C40" s="93" t="s">
         <v>22</v>
       </c>
       <c r="D40" s="4">
@@ -4381,7 +4371,7 @@
       <c r="H40" s="4">
         <v>0</v>
       </c>
-      <c r="I40" s="123">
+      <c r="I40" s="21">
         <v>1</v>
       </c>
       <c r="J40" s="20"/>

--- a/patterns/results/exp2/go-tradeoffs-results.xlsx
+++ b/patterns/results/exp2/go-tradeoffs-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FA470F-8B2A-F543-84EB-A6BC41711F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B283449-2EA1-3E41-852A-29208EBCC98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="1060" windowWidth="34460" windowHeight="16660" activeTab="1" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="9840" yWindow="2120" windowWidth="28560" windowHeight="18440" activeTab="2" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO-2BINS" sheetId="1" r:id="rId1"/>
@@ -250,7 +250,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +311,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="29">
     <border>
@@ -652,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -703,6 +709,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -737,7 +744,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -793,6 +799,8 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1344,453 +1352,453 @@
       <c r="G1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="72"/>
+      <c r="C2" s="73"/>
       <c r="D2" s="14"/>
       <c r="E2" s="38">
         <v>0</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="125">
         <v>1</v>
       </c>
-      <c r="G2" s="69">
-        <v>0</v>
-      </c>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
+      <c r="G2" s="70">
+        <v>0</v>
+      </c>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="74">
+      <c r="C3" s="74"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="75">
         <v>0.11111111111111099</v>
       </c>
-      <c r="F3" s="55">
-        <v>0</v>
-      </c>
-      <c r="G3" s="75">
+      <c r="F3" s="56">
+        <v>0</v>
+      </c>
+      <c r="G3" s="76">
         <v>0.88888888888888795</v>
       </c>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="54"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="55"/>
     </row>
     <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="55">
+      <c r="C4" s="74"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="75">
         <v>0.1</v>
       </c>
-      <c r="F4" s="74">
+      <c r="F4" s="75">
         <v>0.7</v>
       </c>
-      <c r="G4" s="75">
+      <c r="G4" s="76">
         <v>0.2</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="55"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="52" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="14"/>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <v>0</v>
       </c>
       <c r="F5" s="38">
         <v>0</v>
       </c>
-      <c r="G5" s="69">
-        <v>0</v>
-      </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="54"/>
+      <c r="G5" s="70">
+        <v>0</v>
+      </c>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="55"/>
+      <c r="V5" s="55"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="55" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="64"/>
+      <c r="D6" s="65"/>
       <c r="E6" s="79">
         <v>0.11111111111111099</v>
       </c>
-      <c r="F6" s="55">
-        <v>0</v>
-      </c>
-      <c r="G6" s="76">
+      <c r="F6" s="56">
+        <v>0</v>
+      </c>
+      <c r="G6" s="124">
         <v>0.88888888888888795</v>
       </c>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="54"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="55"/>
+      <c r="V6" s="55"/>
     </row>
     <row r="7" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="55" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="45">
-        <v>0</v>
-      </c>
-      <c r="F7" s="55">
+      <c r="E7" s="80">
+        <v>0</v>
+      </c>
+      <c r="F7" s="56">
         <v>0</v>
       </c>
       <c r="G7" s="77">
         <v>0</v>
       </c>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="54"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="57"/>
+      <c r="U7" s="55"/>
+      <c r="V7" s="55"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="16"/>
-      <c r="E8" s="55">
-        <v>0</v>
-      </c>
-      <c r="F8" s="47">
+      <c r="E8" s="56">
+        <v>0</v>
+      </c>
+      <c r="F8" s="44">
         <v>1</v>
       </c>
       <c r="G8" s="78">
         <v>0</v>
       </c>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="60"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="55"/>
+      <c r="V8" s="55"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="55">
+      <c r="D9" s="65"/>
+      <c r="E9" s="56">
         <v>0</v>
       </c>
       <c r="F9" s="79">
         <v>0</v>
       </c>
-      <c r="G9" s="71">
-        <v>0</v>
-      </c>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="59"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
+      <c r="G9" s="72">
+        <v>0</v>
+      </c>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="56"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="55"/>
+      <c r="V9" s="55"/>
     </row>
     <row r="10" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="44">
-        <v>0</v>
-      </c>
-      <c r="F10" s="80">
-        <v>0</v>
-      </c>
-      <c r="G10" s="71">
-        <v>0</v>
-      </c>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
+      <c r="E10" s="45">
+        <v>0</v>
+      </c>
+      <c r="F10" s="46">
+        <v>0</v>
+      </c>
+      <c r="G10" s="72">
+        <v>0</v>
+      </c>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="55"/>
+      <c r="V10" s="55"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="55" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="55">
-        <v>0</v>
-      </c>
-      <c r="F11" s="55">
-        <v>0</v>
-      </c>
-      <c r="G11" s="47">
-        <v>0</v>
-      </c>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="55"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="55"/>
-      <c r="P11" s="55"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="56">
+        <v>0</v>
+      </c>
+      <c r="F11" s="56">
+        <v>0</v>
+      </c>
+      <c r="G11" s="48">
+        <v>0</v>
+      </c>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="55"/>
+      <c r="V11" s="55"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="55" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="55">
+      <c r="D12" s="65"/>
+      <c r="E12" s="56">
         <v>0.11111111111111099</v>
       </c>
-      <c r="F12" s="55">
+      <c r="F12" s="56">
         <v>0</v>
       </c>
       <c r="G12" s="79">
         <v>0.88888888888888795</v>
       </c>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="59"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="50" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="55">
-        <v>0</v>
-      </c>
-      <c r="F13" s="55">
+      <c r="D13" s="65"/>
+      <c r="E13" s="56">
+        <v>0</v>
+      </c>
+      <c r="F13" s="56">
         <v>0</v>
       </c>
       <c r="G13" s="81">
         <v>0</v>
       </c>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="54"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="59"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="55"/>
+      <c r="V13" s="55"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="52" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="111" t="s">
@@ -1800,177 +1808,177 @@
       <c r="E14" s="38">
         <v>0</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="48">
         <v>1</v>
       </c>
-      <c r="G14" s="69">
-        <v>0</v>
-      </c>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="54"/>
-      <c r="V14" s="54"/>
+      <c r="G14" s="70">
+        <v>0</v>
+      </c>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="55"/>
+      <c r="V14" s="55"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="111" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="85"/>
-      <c r="E15" s="55">
+      <c r="E15" s="56">
         <v>0</v>
       </c>
       <c r="F15" s="79">
         <v>0</v>
       </c>
-      <c r="G15" s="71">
-        <v>0</v>
-      </c>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="56"/>
-      <c r="U15" s="54"/>
-      <c r="V15" s="54"/>
+      <c r="G15" s="72">
+        <v>0</v>
+      </c>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="56"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="59"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="55"/>
+      <c r="V15" s="55"/>
     </row>
     <row r="16" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="55" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="111" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="83"/>
-      <c r="E16" s="44">
+      <c r="E16" s="45">
         <v>0</v>
       </c>
       <c r="F16" s="80">
         <v>0</v>
       </c>
-      <c r="G16" s="71">
-        <v>0</v>
-      </c>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="59"/>
-      <c r="T16" s="56"/>
-      <c r="U16" s="54"/>
-      <c r="V16" s="54"/>
+      <c r="G16" s="72">
+        <v>0</v>
+      </c>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="55"/>
+      <c r="V16" s="55"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="55" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="112" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="84"/>
-      <c r="E17" s="46">
-        <v>0</v>
-      </c>
-      <c r="F17" s="55">
+      <c r="E17" s="47">
+        <v>0</v>
+      </c>
+      <c r="F17" s="56">
         <v>1</v>
       </c>
-      <c r="G17" s="47">
-        <v>0</v>
-      </c>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="56"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
+      <c r="G17" s="48">
+        <v>0</v>
+      </c>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="56"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="55"/>
+      <c r="V17" s="55"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="70" t="s">
+      <c r="A18" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="85"/>
-      <c r="E18" s="55">
-        <v>0</v>
-      </c>
-      <c r="F18" s="55">
+      <c r="E18" s="56">
+        <v>0</v>
+      </c>
+      <c r="F18" s="56">
         <v>0</v>
       </c>
       <c r="G18" s="86">
         <v>1</v>
       </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="56"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="54"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="59"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="56"/>
+      <c r="R18" s="56"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="55"/>
+      <c r="V18" s="55"/>
     </row>
     <row r="19" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="50" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="114" t="s">
@@ -1986,453 +1994,453 @@
       <c r="G19" s="80">
         <v>0</v>
       </c>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="59"/>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="56"/>
-      <c r="U19" s="54"/>
-      <c r="V19" s="54"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="56"/>
+      <c r="Q19" s="56"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="55"/>
+      <c r="V19" s="55"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="55"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="56"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="54"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="56"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="56"/>
+      <c r="R20" s="56"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="55"/>
+      <c r="V20" s="55"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" s="54"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="56"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="56"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="54"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="56"/>
-      <c r="U22" s="54"/>
-      <c r="V22" s="54"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="56"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="55"/>
+      <c r="V22" s="55"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A23" s="54"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="56"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="54"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="56"/>
+      <c r="R23" s="56"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="55"/>
+      <c r="V23" s="55"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="60"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="56"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="54"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="56"/>
+      <c r="R24" s="56"/>
+      <c r="S24" s="59"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="55"/>
+      <c r="V24" s="55"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A25" s="54"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="59"/>
-      <c r="T25" s="56"/>
-      <c r="U25" s="54"/>
-      <c r="V25" s="54"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="61"/>
+      <c r="R25" s="56"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="55"/>
+      <c r="V25" s="55"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" s="54"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
-      <c r="R26" s="54"/>
-      <c r="S26" s="54"/>
-      <c r="T26" s="54"/>
-      <c r="U26" s="54"/>
-      <c r="V26" s="54"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="55"/>
+      <c r="P26" s="55"/>
+      <c r="Q26" s="55"/>
+      <c r="R26" s="55"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="55"/>
+      <c r="U26" s="55"/>
+      <c r="V26" s="55"/>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A27" s="54"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-      <c r="R27" s="54"/>
-      <c r="S27" s="54"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-      <c r="V27" s="54"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="55"/>
+      <c r="Q27" s="55"/>
+      <c r="R27" s="55"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="55"/>
+      <c r="V27" s="55"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A28" s="54"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="56"/>
-      <c r="M28" s="56"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="54"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="55"/>
+      <c r="U28" s="55"/>
+      <c r="V28" s="55"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A29" s="54"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="54"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="54"/>
-      <c r="V29" s="54"/>
+      <c r="A29" s="55"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="55"/>
+      <c r="R29" s="55"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="55"/>
+      <c r="V29" s="55"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A30" s="54"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="54"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="54"/>
-      <c r="M30" s="54"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="54"/>
-      <c r="Q30" s="54"/>
-      <c r="R30" s="54"/>
-      <c r="S30" s="54"/>
-      <c r="T30" s="54"/>
-      <c r="U30" s="54"/>
-      <c r="V30" s="54"/>
+      <c r="A30" s="55"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="55"/>
+      <c r="R30" s="55"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="55"/>
+      <c r="V30" s="55"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A31" s="54"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="54"/>
-      <c r="V31" s="54"/>
+      <c r="A31" s="55"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="55"/>
+      <c r="V31" s="55"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A32" s="54"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="54"/>
-      <c r="M32" s="54"/>
-      <c r="N32" s="54"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="54"/>
-      <c r="R32" s="54"/>
-      <c r="S32" s="54"/>
-      <c r="T32" s="54"/>
-      <c r="U32" s="54"/>
-      <c r="V32" s="54"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="55"/>
+      <c r="U32" s="55"/>
+      <c r="V32" s="55"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" s="54"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="54"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="54"/>
-      <c r="R33" s="54"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="54"/>
-      <c r="U33" s="54"/>
-      <c r="V33" s="54"/>
+      <c r="A33" s="55"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="55"/>
+      <c r="U33" s="55"/>
+      <c r="V33" s="55"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="54"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="54"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="54"/>
-      <c r="N34" s="54"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="54"/>
-      <c r="Q34" s="54"/>
-      <c r="R34" s="54"/>
-      <c r="S34" s="54"/>
-      <c r="T34" s="54"/>
-      <c r="U34" s="54"/>
-      <c r="V34" s="54"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="55"/>
+      <c r="N34" s="55"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="55"/>
+      <c r="Q34" s="55"/>
+      <c r="R34" s="55"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="55"/>
+      <c r="U34" s="55"/>
+      <c r="V34" s="55"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="54"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="54"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="55"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="55"/>
+      <c r="R35" s="55"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="55"/>
+      <c r="U35" s="55"/>
+      <c r="V35" s="55"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="54"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="54"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="54"/>
-      <c r="N36" s="54"/>
-      <c r="O36" s="54"/>
-      <c r="P36" s="54"/>
-      <c r="Q36" s="54"/>
-      <c r="R36" s="54"/>
-      <c r="S36" s="54"/>
-      <c r="T36" s="54"/>
-      <c r="U36" s="54"/>
-      <c r="V36" s="54"/>
+      <c r="A36" s="55"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="55"/>
+      <c r="U36" s="55"/>
+      <c r="V36" s="55"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="54"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="54"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="54"/>
-      <c r="S37" s="54"/>
-      <c r="T37" s="54"/>
-      <c r="U37" s="54"/>
-      <c r="V37" s="54"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="55"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="55"/>
+      <c r="R37" s="55"/>
+      <c r="S37" s="55"/>
+      <c r="T37" s="55"/>
+      <c r="U37" s="55"/>
+      <c r="V37" s="55"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B14:G19">
@@ -2491,19 +2499,19 @@
       <c r="G1" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="55"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
@@ -2525,53 +2533,53 @@
       <c r="G2" s="101">
         <v>1</v>
       </c>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="91"/>
-      <c r="D3" s="56">
-        <v>0</v>
-      </c>
-      <c r="E3" s="74">
+      <c r="D3" s="57">
+        <v>0</v>
+      </c>
+      <c r="E3" s="75">
         <v>0.44444444444444398</v>
       </c>
-      <c r="F3" s="74">
+      <c r="F3" s="75">
         <v>0.55555555555555503</v>
       </c>
       <c r="G3" s="96">
         <v>0</v>
       </c>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="57"/>
     </row>
     <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
@@ -2581,31 +2589,31 @@
         <v>6</v>
       </c>
       <c r="C4" s="91"/>
-      <c r="D4" s="74">
+      <c r="D4" s="75">
         <v>7.1428571428571397E-2</v>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="75">
         <v>0.64285714285714202</v>
       </c>
-      <c r="F4" s="74">
+      <c r="F4" s="75">
         <v>0.28571428571428498</v>
       </c>
       <c r="G4" s="96">
         <v>0</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="98" t="s">
@@ -2620,238 +2628,238 @@
       <c r="D5" s="38">
         <v>0</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <v>0</v>
       </c>
       <c r="F5" s="38">
         <v>0</v>
       </c>
-      <c r="G5" s="69">
-        <v>0</v>
-      </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="56"/>
+      <c r="G5" s="70">
+        <v>0</v>
+      </c>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="57"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="57" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="56">
         <v>0</v>
       </c>
       <c r="E6" s="81">
         <v>0</v>
       </c>
-      <c r="F6" s="55">
-        <v>0</v>
-      </c>
-      <c r="G6" s="71">
-        <v>0</v>
-      </c>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
+      <c r="F6" s="56">
+        <v>0</v>
+      </c>
+      <c r="G6" s="72">
+        <v>0</v>
+      </c>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="55" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="45">
         <v>0.14285714285714199</v>
       </c>
       <c r="E7" s="103">
         <v>0.85714285714285698</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="56">
         <v>0</v>
       </c>
       <c r="G7" s="77">
         <v>0</v>
       </c>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="57"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="56" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="46">
-        <v>0</v>
-      </c>
-      <c r="E8" s="55">
-        <v>0</v>
-      </c>
-      <c r="F8" s="47">
+      <c r="D8" s="47">
+        <v>0</v>
+      </c>
+      <c r="E8" s="56">
+        <v>0</v>
+      </c>
+      <c r="F8" s="48">
         <v>0</v>
       </c>
       <c r="G8" s="78">
         <v>0</v>
       </c>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="Q8" s="59"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="57" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="55">
-        <v>0</v>
-      </c>
-      <c r="E9" s="67">
+      <c r="D9" s="56">
+        <v>0</v>
+      </c>
+      <c r="E9" s="68">
         <v>0.44444444444444398</v>
       </c>
       <c r="F9" s="79">
         <v>0.55555555555555503</v>
       </c>
-      <c r="G9" s="71">
-        <v>0</v>
-      </c>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="Q9" s="59"/>
-      <c r="R9" s="56"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="56"/>
+      <c r="G9" s="72">
+        <v>0</v>
+      </c>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="57"/>
     </row>
     <row r="10" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="55" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="44">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44">
+      <c r="D10" s="45">
+        <v>0</v>
+      </c>
+      <c r="E10" s="45">
         <v>0</v>
       </c>
       <c r="F10" s="80">
         <v>0</v>
       </c>
-      <c r="G10" s="71">
-        <v>0</v>
-      </c>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
+      <c r="G10" s="72">
+        <v>0</v>
+      </c>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="57"/>
+      <c r="T10" s="57"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="57" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="55">
-        <v>0</v>
-      </c>
-      <c r="E11" s="55">
-        <v>0</v>
-      </c>
-      <c r="F11" s="55">
-        <v>0</v>
-      </c>
-      <c r="G11" s="47">
+      <c r="D11" s="56">
+        <v>0</v>
+      </c>
+      <c r="E11" s="56">
+        <v>0</v>
+      </c>
+      <c r="F11" s="56">
+        <v>0</v>
+      </c>
+      <c r="G11" s="48">
         <v>1</v>
       </c>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="Q11" s="56"/>
-      <c r="R11" s="59"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="56"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="60"/>
+      <c r="S11" s="61"/>
+      <c r="T11" s="57"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="55">
-        <v>0</v>
-      </c>
-      <c r="E12" s="55">
-        <v>0</v>
-      </c>
-      <c r="F12" s="55">
+      <c r="D12" s="56">
+        <v>0</v>
+      </c>
+      <c r="E12" s="56">
+        <v>0</v>
+      </c>
+      <c r="F12" s="56">
         <v>0</v>
       </c>
       <c r="G12" s="79">
         <v>0</v>
       </c>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="59"/>
-      <c r="T12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="57"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="57"/>
     </row>
     <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -2875,12 +2883,12 @@
       <c r="G13" s="34">
         <v>0</v>
       </c>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="56"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="57"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2904,41 +2912,41 @@
       <c r="G14" s="32">
         <v>1</v>
       </c>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="56"/>
-      <c r="T14" s="56"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="Q14" s="59"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="65">
-        <v>0</v>
-      </c>
-      <c r="E15" s="65">
-        <v>0</v>
-      </c>
-      <c r="F15" s="65">
+      <c r="D15" s="66">
+        <v>0</v>
+      </c>
+      <c r="E15" s="66">
+        <v>0</v>
+      </c>
+      <c r="F15" s="66">
         <v>0</v>
       </c>
       <c r="G15" s="33">
         <v>0</v>
       </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="56"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="56"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="57"/>
     </row>
     <row r="16" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -2962,57 +2970,57 @@
       <c r="G16" s="34">
         <v>0</v>
       </c>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="54"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="55"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="55"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="54"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="54"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="Q18" s="55"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="55"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="Q19" s="61"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="61"/>
-      <c r="T19" s="61"/>
+      <c r="A19" s="62"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="62"/>
+      <c r="T19" s="62"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:G13">
@@ -3092,15 +3100,15 @@
       <c r="K1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="55"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
@@ -3130,53 +3138,53 @@
       </c>
       <c r="J2" s="19"/>
       <c r="K2" s="29"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="56"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="57"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="91"/>
       <c r="D3" s="115">
         <v>0.77777777777777701</v>
       </c>
-      <c r="E3" s="55">
-        <v>0</v>
-      </c>
-      <c r="F3" s="55">
-        <v>0</v>
-      </c>
-      <c r="G3" s="55">
+      <c r="E3" s="56">
+        <v>0</v>
+      </c>
+      <c r="F3" s="56">
+        <v>0</v>
+      </c>
+      <c r="G3" s="56">
         <v>0</v>
       </c>
       <c r="H3" s="115">
         <v>0.22222222222222199</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="57">
         <v>0</v>
       </c>
       <c r="J3" s="118"/>
       <c r="K3" s="30"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
     </row>
     <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
@@ -3206,15 +3214,15 @@
       </c>
       <c r="J4" s="20"/>
       <c r="K4" s="31"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
@@ -3226,7 +3234,7 @@
       <c r="C5" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="48">
         <v>0</v>
       </c>
       <c r="E5" s="38">
@@ -3246,21 +3254,21 @@
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="29"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="92" t="s">
@@ -3269,38 +3277,38 @@
       <c r="D6" s="22">
         <v>1</v>
       </c>
-      <c r="E6" s="66">
-        <v>0</v>
-      </c>
-      <c r="F6" s="66">
-        <v>0</v>
-      </c>
-      <c r="G6" s="66">
-        <v>0</v>
-      </c>
-      <c r="H6" s="66">
-        <v>0</v>
-      </c>
-      <c r="I6" s="66">
+      <c r="E6" s="67">
+        <v>0</v>
+      </c>
+      <c r="F6" s="67">
+        <v>0</v>
+      </c>
+      <c r="G6" s="67">
+        <v>0</v>
+      </c>
+      <c r="H6" s="67">
+        <v>0</v>
+      </c>
+      <c r="I6" s="67">
         <v>0</v>
       </c>
       <c r="J6" s="118"/>
       <c r="K6" s="30"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="119" t="s">
@@ -3309,47 +3317,47 @@
       <c r="D7" s="34">
         <v>0</v>
       </c>
-      <c r="E7" s="66">
-        <v>0</v>
-      </c>
-      <c r="F7" s="66">
-        <v>0</v>
-      </c>
-      <c r="G7" s="66">
-        <v>0</v>
-      </c>
-      <c r="H7" s="66">
-        <v>0</v>
-      </c>
-      <c r="I7" s="66">
+      <c r="E7" s="67">
+        <v>0</v>
+      </c>
+      <c r="F7" s="67">
+        <v>0</v>
+      </c>
+      <c r="G7" s="67">
+        <v>0</v>
+      </c>
+      <c r="H7" s="67">
+        <v>0</v>
+      </c>
+      <c r="I7" s="67">
         <v>0</v>
       </c>
       <c r="J7" s="118"/>
       <c r="K7" s="30"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="55"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="53" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="39">
         <v>0</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <v>0</v>
       </c>
       <c r="F8" s="39">
@@ -3366,61 +3374,61 @@
       </c>
       <c r="J8" s="19"/>
       <c r="K8" s="29"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="55"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="67">
         <v>0</v>
       </c>
       <c r="E9" s="33">
         <v>0</v>
       </c>
-      <c r="F9" s="66">
-        <v>0</v>
-      </c>
-      <c r="G9" s="66">
-        <v>0</v>
-      </c>
-      <c r="H9" s="66">
-        <v>0</v>
-      </c>
-      <c r="I9" s="66">
+      <c r="F9" s="67">
+        <v>0</v>
+      </c>
+      <c r="G9" s="67">
+        <v>0</v>
+      </c>
+      <c r="H9" s="67">
+        <v>0</v>
+      </c>
+      <c r="I9" s="67">
         <v>0</v>
       </c>
       <c r="J9" s="118"/>
       <c r="K9" s="30"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="55"/>
     </row>
     <row r="10" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="93" t="s">
@@ -3451,7 +3459,7 @@
       <c r="A11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="62" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="100" t="s">
@@ -3482,16 +3490,16 @@
       <c r="A12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="66">
-        <v>0</v>
-      </c>
-      <c r="E12" s="66">
+      <c r="D12" s="67">
+        <v>0</v>
+      </c>
+      <c r="E12" s="67">
         <v>0</v>
       </c>
       <c r="F12" s="33">
@@ -3500,10 +3508,10 @@
       <c r="G12" s="122">
         <v>0</v>
       </c>
-      <c r="H12" s="66">
-        <v>0</v>
-      </c>
-      <c r="I12" s="66">
+      <c r="H12" s="67">
+        <v>0</v>
+      </c>
+      <c r="I12" s="67">
         <v>0</v>
       </c>
       <c r="J12" s="118"/>
@@ -3513,7 +3521,7 @@
       <c r="A13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="93" t="s">
@@ -3544,10 +3552,10 @@
       <c r="A14" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="53" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="39">
@@ -3559,7 +3567,7 @@
       <c r="F14" s="39">
         <v>0</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="48">
         <v>1</v>
       </c>
       <c r="H14" s="39">
@@ -3575,28 +3583,28 @@
       <c r="A15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="66">
-        <v>0</v>
-      </c>
-      <c r="E15" s="66">
-        <v>0</v>
-      </c>
-      <c r="F15" s="66">
+      <c r="D15" s="67">
+        <v>0</v>
+      </c>
+      <c r="E15" s="67">
+        <v>0</v>
+      </c>
+      <c r="F15" s="67">
         <v>0</v>
       </c>
       <c r="G15" s="33">
         <v>0</v>
       </c>
-      <c r="H15" s="66">
-        <v>0</v>
-      </c>
-      <c r="I15" s="66">
+      <c r="H15" s="67">
+        <v>0</v>
+      </c>
+      <c r="I15" s="67">
         <v>0</v>
       </c>
       <c r="J15" s="118"/>
@@ -3606,41 +3614,41 @@
       <c r="A16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="66">
-        <v>0</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0</v>
-      </c>
-      <c r="F16" s="66">
+      <c r="D16" s="67">
+        <v>0</v>
+      </c>
+      <c r="E16" s="67">
+        <v>0</v>
+      </c>
+      <c r="F16" s="67">
         <v>0</v>
       </c>
       <c r="G16" s="34">
         <v>0</v>
       </c>
-      <c r="H16" s="66">
-        <v>0</v>
-      </c>
-      <c r="I16" s="66">
+      <c r="H16" s="67">
+        <v>0</v>
+      </c>
+      <c r="I16" s="67">
         <v>0</v>
       </c>
       <c r="J16" s="118"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="73" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="39">
@@ -3655,7 +3663,7 @@
       <c r="G17" s="39">
         <v>0</v>
       </c>
-      <c r="H17" s="47">
+      <c r="H17" s="48">
         <v>0</v>
       </c>
       <c r="I17" s="39">
@@ -3668,28 +3676,28 @@
       <c r="A18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="67">
+      <c r="D18" s="68">
         <v>0.77777777777777701</v>
       </c>
-      <c r="E18" s="66">
-        <v>0</v>
-      </c>
-      <c r="F18" s="66">
-        <v>0</v>
-      </c>
-      <c r="G18" s="66">
+      <c r="E18" s="67">
+        <v>0</v>
+      </c>
+      <c r="F18" s="67">
+        <v>0</v>
+      </c>
+      <c r="G18" s="67">
         <v>0</v>
       </c>
       <c r="H18" s="33">
         <v>0.22222222222222199</v>
       </c>
-      <c r="I18" s="66">
+      <c r="I18" s="67">
         <v>0</v>
       </c>
       <c r="J18" s="118"/>
@@ -3699,7 +3707,7 @@
       <c r="A19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="120" t="s">
@@ -3730,28 +3738,28 @@
       <c r="A20" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="56" t="s">
         <v>4</v>
       </c>
       <c r="C20" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="55">
-        <v>0</v>
-      </c>
-      <c r="E20" s="55">
-        <v>0</v>
-      </c>
-      <c r="F20" s="55">
-        <v>0</v>
-      </c>
-      <c r="G20" s="55">
-        <v>0</v>
-      </c>
-      <c r="H20" s="55">
-        <v>0</v>
-      </c>
-      <c r="I20" s="47">
+      <c r="D20" s="56">
+        <v>0</v>
+      </c>
+      <c r="E20" s="56">
+        <v>0</v>
+      </c>
+      <c r="F20" s="56">
+        <v>0</v>
+      </c>
+      <c r="G20" s="56">
+        <v>0</v>
+      </c>
+      <c r="H20" s="56">
+        <v>0</v>
+      </c>
+      <c r="I20" s="48">
         <v>0</v>
       </c>
       <c r="J20" s="118"/>
@@ -3761,25 +3769,25 @@
       <c r="A21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="66">
-        <v>0</v>
-      </c>
-      <c r="E21" s="66">
-        <v>0</v>
-      </c>
-      <c r="F21" s="66">
-        <v>0</v>
-      </c>
-      <c r="G21" s="66">
-        <v>0</v>
-      </c>
-      <c r="H21" s="66">
+      <c r="D21" s="67">
+        <v>0</v>
+      </c>
+      <c r="E21" s="67">
+        <v>0</v>
+      </c>
+      <c r="F21" s="67">
+        <v>0</v>
+      </c>
+      <c r="G21" s="67">
+        <v>0</v>
+      </c>
+      <c r="H21" s="67">
         <v>0</v>
       </c>
       <c r="I21" s="33">
@@ -3854,7 +3862,7 @@
       <c r="A24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="92" t="s">
@@ -3863,19 +3871,19 @@
       <c r="D24" s="123">
         <v>1</v>
       </c>
-      <c r="E24" s="65">
-        <v>0</v>
-      </c>
-      <c r="F24" s="66">
-        <v>0</v>
-      </c>
-      <c r="G24" s="66">
-        <v>0</v>
-      </c>
-      <c r="H24" s="66">
-        <v>0</v>
-      </c>
-      <c r="I24" s="66">
+      <c r="E24" s="66">
+        <v>0</v>
+      </c>
+      <c r="F24" s="67">
+        <v>0</v>
+      </c>
+      <c r="G24" s="67">
+        <v>0</v>
+      </c>
+      <c r="H24" s="67">
+        <v>0</v>
+      </c>
+      <c r="I24" s="67">
         <v>0</v>
       </c>
       <c r="J24" s="118"/>
@@ -3885,7 +3893,7 @@
       <c r="A25" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="92" t="s">
@@ -3894,19 +3902,19 @@
       <c r="D25" s="34">
         <v>0</v>
       </c>
-      <c r="E25" s="68">
+      <c r="E25" s="69">
         <v>0.33333333333333298</v>
       </c>
-      <c r="F25" s="68">
+      <c r="F25" s="69">
         <v>0.66666666666666596</v>
       </c>
-      <c r="G25" s="66">
-        <v>0</v>
-      </c>
-      <c r="H25" s="66">
-        <v>0</v>
-      </c>
-      <c r="I25" s="66">
+      <c r="G25" s="67">
+        <v>0</v>
+      </c>
+      <c r="H25" s="67">
+        <v>0</v>
+      </c>
+      <c r="I25" s="67">
         <v>0</v>
       </c>
       <c r="J25" s="118"/>
@@ -3916,28 +3924,28 @@
       <c r="A26" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="62" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="67">
         <v>0</v>
       </c>
       <c r="E26" s="32">
         <v>0</v>
       </c>
-      <c r="F26" s="66">
-        <v>0</v>
-      </c>
-      <c r="G26" s="66">
-        <v>0</v>
-      </c>
-      <c r="H26" s="66">
-        <v>0</v>
-      </c>
-      <c r="I26" s="66">
+      <c r="F26" s="67">
+        <v>0</v>
+      </c>
+      <c r="G26" s="67">
+        <v>0</v>
+      </c>
+      <c r="H26" s="67">
+        <v>0</v>
+      </c>
+      <c r="I26" s="67">
         <v>0</v>
       </c>
       <c r="J26" s="118"/>
@@ -3947,28 +3955,28 @@
       <c r="A27" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="66">
+      <c r="D27" s="67">
         <v>0</v>
       </c>
       <c r="E27" s="33">
         <v>0</v>
       </c>
-      <c r="F27" s="66">
-        <v>0</v>
-      </c>
-      <c r="G27" s="66">
-        <v>0</v>
-      </c>
-      <c r="H27" s="66">
-        <v>0</v>
-      </c>
-      <c r="I27" s="66">
+      <c r="F27" s="67">
+        <v>0</v>
+      </c>
+      <c r="G27" s="67">
+        <v>0</v>
+      </c>
+      <c r="H27" s="67">
+        <v>0</v>
+      </c>
+      <c r="I27" s="67">
         <v>0</v>
       </c>
       <c r="J27" s="118"/>
@@ -3978,28 +3986,28 @@
       <c r="A28" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="67">
         <v>0</v>
       </c>
       <c r="E28" s="21">
         <v>1</v>
       </c>
-      <c r="F28" s="66">
-        <v>0</v>
-      </c>
-      <c r="G28" s="66">
-        <v>0</v>
-      </c>
-      <c r="H28" s="66">
-        <v>0</v>
-      </c>
-      <c r="I28" s="66">
+      <c r="F28" s="67">
+        <v>0</v>
+      </c>
+      <c r="G28" s="67">
+        <v>0</v>
+      </c>
+      <c r="H28" s="67">
+        <v>0</v>
+      </c>
+      <c r="I28" s="67">
         <v>0</v>
       </c>
       <c r="J28" s="118"/>
@@ -4009,28 +4017,28 @@
       <c r="A29" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="62" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="66">
-        <v>0</v>
-      </c>
-      <c r="E29" s="66">
+      <c r="D29" s="67">
+        <v>0</v>
+      </c>
+      <c r="E29" s="67">
         <v>0</v>
       </c>
       <c r="F29" s="32">
         <v>0</v>
       </c>
-      <c r="G29" s="66">
-        <v>0</v>
-      </c>
-      <c r="H29" s="66">
-        <v>0</v>
-      </c>
-      <c r="I29" s="66">
+      <c r="G29" s="67">
+        <v>0</v>
+      </c>
+      <c r="H29" s="67">
+        <v>0</v>
+      </c>
+      <c r="I29" s="67">
         <v>0</v>
       </c>
       <c r="J29" s="118"/>
@@ -4040,28 +4048,28 @@
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="66">
-        <v>0</v>
-      </c>
-      <c r="E30" s="66">
+      <c r="D30" s="67">
+        <v>0</v>
+      </c>
+      <c r="E30" s="67">
         <v>0</v>
       </c>
       <c r="F30" s="33">
         <v>0</v>
       </c>
-      <c r="G30" s="66">
-        <v>0</v>
-      </c>
-      <c r="H30" s="66">
-        <v>0</v>
-      </c>
-      <c r="I30" s="66">
+      <c r="G30" s="67">
+        <v>0</v>
+      </c>
+      <c r="H30" s="67">
+        <v>0</v>
+      </c>
+      <c r="I30" s="67">
         <v>0</v>
       </c>
       <c r="J30" s="118"/>
@@ -4071,28 +4079,28 @@
       <c r="A31" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="66">
-        <v>0</v>
-      </c>
-      <c r="E31" s="66">
+      <c r="D31" s="67">
+        <v>0</v>
+      </c>
+      <c r="E31" s="67">
         <v>0</v>
       </c>
       <c r="F31" s="21">
         <v>1</v>
       </c>
-      <c r="G31" s="66">
-        <v>0</v>
-      </c>
-      <c r="H31" s="66">
-        <v>0</v>
-      </c>
-      <c r="I31" s="66">
+      <c r="G31" s="67">
+        <v>0</v>
+      </c>
+      <c r="H31" s="67">
+        <v>0</v>
+      </c>
+      <c r="I31" s="67">
         <v>0</v>
       </c>
       <c r="J31" s="118"/>
@@ -4102,28 +4110,28 @@
       <c r="A32" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="62" t="s">
         <v>4</v>
       </c>
       <c r="C32" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="66">
-        <v>0</v>
-      </c>
-      <c r="E32" s="66">
-        <v>0</v>
-      </c>
-      <c r="F32" s="66">
+      <c r="D32" s="67">
+        <v>0</v>
+      </c>
+      <c r="E32" s="67">
+        <v>0</v>
+      </c>
+      <c r="F32" s="67">
         <v>0</v>
       </c>
       <c r="G32" s="32">
         <v>1</v>
       </c>
-      <c r="H32" s="66">
-        <v>0</v>
-      </c>
-      <c r="I32" s="66">
+      <c r="H32" s="67">
+        <v>0</v>
+      </c>
+      <c r="I32" s="67">
         <v>0</v>
       </c>
       <c r="J32" s="118"/>
@@ -4133,28 +4141,28 @@
       <c r="A33" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="66">
-        <v>0</v>
-      </c>
-      <c r="E33" s="66">
-        <v>0</v>
-      </c>
-      <c r="F33" s="66">
+      <c r="D33" s="67">
+        <v>0</v>
+      </c>
+      <c r="E33" s="67">
+        <v>0</v>
+      </c>
+      <c r="F33" s="67">
         <v>0</v>
       </c>
       <c r="G33" s="33">
         <v>0</v>
       </c>
-      <c r="H33" s="66">
-        <v>0</v>
-      </c>
-      <c r="I33" s="66">
+      <c r="H33" s="67">
+        <v>0</v>
+      </c>
+      <c r="I33" s="67">
         <v>0</v>
       </c>
       <c r="J33" s="118"/>
@@ -4164,28 +4172,28 @@
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="61" t="s">
+      <c r="B34" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="66">
-        <v>0</v>
-      </c>
-      <c r="E34" s="66">
-        <v>0</v>
-      </c>
-      <c r="F34" s="66">
+      <c r="D34" s="67">
+        <v>0</v>
+      </c>
+      <c r="E34" s="67">
+        <v>0</v>
+      </c>
+      <c r="F34" s="67">
         <v>0</v>
       </c>
       <c r="G34" s="34">
         <v>0</v>
       </c>
-      <c r="H34" s="66">
-        <v>0</v>
-      </c>
-      <c r="I34" s="66">
+      <c r="H34" s="67">
+        <v>0</v>
+      </c>
+      <c r="I34" s="67">
         <v>0</v>
       </c>
       <c r="J34" s="118"/>
@@ -4195,28 +4203,28 @@
       <c r="A35" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="61" t="s">
+      <c r="B35" s="62" t="s">
         <v>4</v>
       </c>
       <c r="C35" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="66">
-        <v>0</v>
-      </c>
-      <c r="E35" s="66">
-        <v>0</v>
-      </c>
-      <c r="F35" s="66">
-        <v>0</v>
-      </c>
-      <c r="G35" s="66">
+      <c r="D35" s="67">
+        <v>0</v>
+      </c>
+      <c r="E35" s="67">
+        <v>0</v>
+      </c>
+      <c r="F35" s="67">
+        <v>0</v>
+      </c>
+      <c r="G35" s="67">
         <v>1</v>
       </c>
       <c r="H35" s="32">
         <v>0</v>
       </c>
-      <c r="I35" s="66">
+      <c r="I35" s="67">
         <v>0</v>
       </c>
       <c r="J35" s="118"/>
@@ -4226,28 +4234,28 @@
       <c r="A36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="61" t="s">
+      <c r="B36" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="66">
-        <v>0</v>
-      </c>
-      <c r="E36" s="66">
-        <v>0</v>
-      </c>
-      <c r="F36" s="66">
-        <v>0</v>
-      </c>
-      <c r="G36" s="66">
+      <c r="D36" s="67">
+        <v>0</v>
+      </c>
+      <c r="E36" s="67">
+        <v>0</v>
+      </c>
+      <c r="F36" s="67">
+        <v>0</v>
+      </c>
+      <c r="G36" s="67">
         <v>0</v>
       </c>
       <c r="H36" s="22">
         <v>1</v>
       </c>
-      <c r="I36" s="66">
+      <c r="I36" s="67">
         <v>0</v>
       </c>
       <c r="J36" s="118"/>
@@ -4257,28 +4265,28 @@
       <c r="A37" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="61" t="s">
+      <c r="B37" s="62" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="66">
-        <v>0</v>
-      </c>
-      <c r="E37" s="66">
-        <v>0</v>
-      </c>
-      <c r="F37" s="66">
-        <v>0</v>
-      </c>
-      <c r="G37" s="66">
+      <c r="D37" s="67">
+        <v>0</v>
+      </c>
+      <c r="E37" s="67">
+        <v>0</v>
+      </c>
+      <c r="F37" s="67">
+        <v>0</v>
+      </c>
+      <c r="G37" s="67">
         <v>0</v>
       </c>
       <c r="H37" s="34">
         <v>0</v>
       </c>
-      <c r="I37" s="66">
+      <c r="I37" s="67">
         <v>1</v>
       </c>
       <c r="J37" s="118"/>
@@ -4288,25 +4296,25 @@
       <c r="A38" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="62" t="s">
         <v>4</v>
       </c>
       <c r="C38" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="66">
-        <v>0</v>
-      </c>
-      <c r="E38" s="66">
-        <v>0</v>
-      </c>
-      <c r="F38" s="66">
-        <v>0</v>
-      </c>
-      <c r="G38" s="66">
-        <v>0</v>
-      </c>
-      <c r="H38" s="66">
+      <c r="D38" s="67">
+        <v>0</v>
+      </c>
+      <c r="E38" s="67">
+        <v>0</v>
+      </c>
+      <c r="F38" s="67">
+        <v>0</v>
+      </c>
+      <c r="G38" s="67">
+        <v>0</v>
+      </c>
+      <c r="H38" s="67">
         <v>0</v>
       </c>
       <c r="I38" s="32">
@@ -4319,25 +4327,25 @@
       <c r="A39" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="61" t="s">
+      <c r="B39" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="66">
-        <v>0</v>
-      </c>
-      <c r="E39" s="66">
-        <v>0</v>
-      </c>
-      <c r="F39" s="66">
-        <v>0</v>
-      </c>
-      <c r="G39" s="66">
-        <v>0</v>
-      </c>
-      <c r="H39" s="66">
+      <c r="D39" s="67">
+        <v>0</v>
+      </c>
+      <c r="E39" s="67">
+        <v>0</v>
+      </c>
+      <c r="F39" s="67">
+        <v>0</v>
+      </c>
+      <c r="G39" s="67">
+        <v>0</v>
+      </c>
+      <c r="H39" s="67">
         <v>0</v>
       </c>
       <c r="I39" s="33">
